--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6CA573-04D2-3C47-8990-C2AFA58BEC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F009FE09-8329-8B41-A2AE-FA7512C1800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2460" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="161">
   <si>
     <t>brand</t>
   </si>
@@ -501,6 +501,21 @@
   </si>
   <si>
     <t>no_offset_fork_length</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
   </si>
 </sst>
 </file>
@@ -869,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -3033,10 +3048,10 @@
     </row>
     <row r="35" spans="1:39">
       <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>156</v>
+      </c>
+      <c r="B35" t="s">
+        <v>157</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
@@ -3063,10 +3078,10 @@
     </row>
     <row r="36" spans="1:39">
       <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>66</v>
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -3093,7 +3108,10 @@
     </row>
     <row r="37" spans="1:39">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>129</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>96</v>
@@ -3126,10 +3144,10 @@
     </row>
     <row r="38" spans="1:39">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38">
-        <v>54</v>
+        <v>30</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3170,9 +3188,11 @@
     </row>
     <row r="39" spans="1:39">
       <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="E39">
         <f>((622 + 2*E29)/2*COS(E10*PI()/180) - E17)/SIN(E10*PI()/180)</f>
         <v>78.184365946303487</v>
@@ -3220,7 +3240,7 @@
     </row>
     <row r="40" spans="1:39" ht="21">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C40" s="2"/>
       <c r="J40" s="7"/>
@@ -3230,10 +3250,10 @@
     </row>
     <row r="41" spans="1:39">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="B41">
+        <v>54</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>102</v>
@@ -3247,8 +3267,9 @@
     </row>
     <row r="42" spans="1:39">
       <c r="A42" t="s">
-        <v>37</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B42" s="1"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3259,7 +3280,7 @@
     </row>
     <row r="43" spans="1:39">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>104</v>
@@ -3292,7 +3313,10 @@
     </row>
     <row r="44" spans="1:39">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
@@ -3319,7 +3343,7 @@
     </row>
     <row r="45" spans="1:39">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AI45" s="4" t="s">
         <v>148</v>
@@ -3343,10 +3367,7 @@
     </row>
     <row r="46" spans="1:39">
       <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="AI46" s="4" t="s">
         <v>23</v>
@@ -3370,7 +3391,7 @@
     </row>
     <row r="47" spans="1:39">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>109</v>
@@ -3397,113 +3418,107 @@
     </row>
     <row r="48" spans="1:39">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50">
         <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="B53">
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B54" s="1"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="1"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>126</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>66</v>
@@ -3511,7 +3526,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>66</v>
@@ -3519,23 +3534,23 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66">
-        <v>2399</v>
+        <v>58</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67">
-        <v>4975</v>
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>66</v>
@@ -3543,19 +3558,38 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3572,6 +3606,11 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F009FE09-8329-8B41-A2AE-FA7512C1800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EE5256-C7B4-0D42-9987-19466A3FD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="161">
   <si>
     <t>brand</t>
   </si>
@@ -3315,9 +3315,7 @@
       <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B44" s="1"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3590,6 +3588,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3606,11 +3609,6 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EE5256-C7B4-0D42-9987-19466A3FD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A5CC20-6DAC-B540-9BCC-9F28F599C4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="162">
   <si>
     <t>brand</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>fork</t>
+  </si>
+  <si>
+    <t>https://litespeed.com/cdn/shop/files/flint-bike-feature-image_45e86c2c-6887-4c01-8170-2e8c17d83903.png?v=1752259609</t>
   </si>
 </sst>
 </file>
@@ -931,6 +934,11 @@
         <v>133</v>
       </c>
     </row>
+    <row r="6" spans="1:39">
+      <c r="B6" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
     <row r="7" spans="1:39">
       <c r="A7" t="s">
         <v>5</v>
@@ -3588,11 +3596,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3609,6 +3612,11 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A5CC20-6DAC-B540-9BCC-9F28F599C4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA11123-1FA4-7F4E-B60E-05994EB69497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="164">
   <si>
     <t>brand</t>
   </si>
@@ -236,9 +236,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -519,6 +516,15 @@
   </si>
   <si>
     <t>https://litespeed.com/cdn/shop/files/flint-bike-feature-image_45e86c2c-6887-4c01-8170-2e8c17d83903.png?v=1752259609</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Chattanooga, Tennessee, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -887,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -899,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:39">
@@ -907,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:39">
@@ -931,12 +937,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:39">
       <c r="B6" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:39">
@@ -944,13 +950,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:39">
@@ -958,104 +964,104 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="T8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="U8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="V8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="W8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="X8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="Y8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Z8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="AA8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AA8" s="4" t="s">
+      <c r="AB8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AB8" s="4" t="s">
+      <c r="AC8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AC8" s="4" t="s">
+      <c r="AD8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AD8" s="4" t="s">
+      <c r="AE8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AE8" s="4" t="s">
+      <c r="AF8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AF8" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="AI8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AJ8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AK8" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="AL8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM8" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:39">
@@ -1063,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5">
         <f>J9*10</f>
@@ -1109,16 +1115,16 @@
         <v>60</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R9" s="5">
         <v>50.3</v>
       </c>
       <c r="S9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="T9" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="U9" s="5">
         <v>43</v>
@@ -1145,10 +1151,10 @@
         <v>10.1</v>
       </c>
       <c r="AC9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD9" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="AE9" s="5">
         <v>80</v>
@@ -1157,7 +1163,7 @@
         <v>170</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AJ9" s="5">
         <v>545</v>
@@ -1177,7 +1183,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" s="5">
         <f>J10</f>
@@ -1223,16 +1229,16 @@
         <v>71.5</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R10" s="5">
         <v>52.3</v>
       </c>
       <c r="S10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="U10" s="5">
         <v>44.5</v>
@@ -1271,7 +1277,7 @@
         <v>170</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AJ10" s="5">
         <v>70</v>
@@ -1291,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="5">
         <f>J11</f>
@@ -1337,16 +1343,16 @@
         <v>73</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R11" s="5">
         <v>54.5</v>
       </c>
       <c r="S11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T11" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="U11" s="5">
         <v>47</v>
@@ -1385,7 +1391,7 @@
         <v>170</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AJ11" s="5">
         <v>74</v>
@@ -1405,7 +1411,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="5">
         <f t="shared" ref="C12:C21" si="2">J12*10</f>
@@ -1451,16 +1457,16 @@
         <v>55</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R12" s="5">
         <v>56.8</v>
       </c>
       <c r="S12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="T12" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="U12" s="5">
         <v>49.5</v>
@@ -1499,7 +1505,7 @@
         <v>170</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ12" s="5">
         <v>470</v>
@@ -1519,7 +1525,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" s="5">
         <f t="shared" si="2"/>
@@ -1565,16 +1571,16 @@
         <v>43.7</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R13" s="5">
         <v>58</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U13" s="5">
         <v>52</v>
@@ -1613,7 +1619,7 @@
         <v>175</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ13" s="5">
         <v>437</v>
@@ -1633,7 +1639,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" s="5">
         <f t="shared" si="2"/>
@@ -1679,16 +1685,16 @@
         <v>7.4</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R14" s="5">
         <v>60</v>
       </c>
       <c r="S14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="T14" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="U14" s="5">
         <v>55</v>
@@ -1727,7 +1733,7 @@
         <v>175</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ14" s="5">
         <v>76</v>
@@ -1747,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" si="2"/>
@@ -1793,10 +1799,10 @@
         <v>107.5</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AJ15" s="5">
         <v>1045</v>
@@ -1816,7 +1822,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="5">
         <f t="shared" si="2"/>
@@ -1863,52 +1869,52 @@
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="T16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="Y16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Y16" s="4" t="s">
+      <c r="Z16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Z16" s="4" t="s">
+      <c r="AA16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AA16" s="4" t="s">
+      <c r="AB16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AB16" s="4" t="s">
+      <c r="AC16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AC16" s="4" t="s">
+      <c r="AD16" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AD16" s="4" t="s">
+      <c r="AE16" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AE16" s="4" t="s">
+      <c r="AF16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AF16" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="AI16" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ16" s="5">
         <v>620</v>
@@ -1928,7 +1934,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5">
         <f t="shared" si="2"/>
@@ -1974,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R17" s="5">
         <v>50.3</v>
       </c>
       <c r="S17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="T17" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="U17" s="5">
         <v>43</v>
@@ -2010,10 +2016,10 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="AC17" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD17" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="AD17" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="AE17" s="5">
         <v>80</v>
@@ -2022,7 +2028,7 @@
         <v>170</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ17" s="5">
         <v>50</v>
@@ -2042,7 +2048,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="5">
         <f t="shared" si="2"/>
@@ -2088,16 +2094,16 @@
         <v>83.8</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R18" s="5">
         <v>52.3</v>
       </c>
       <c r="S18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="T18" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="U18" s="5">
         <v>44.5</v>
@@ -2136,7 +2142,7 @@
         <v>170</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AJ18" s="5">
         <v>758</v>
@@ -2156,7 +2162,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" s="5">
         <f t="shared" si="2"/>
@@ -2202,16 +2208,16 @@
         <v>21.4</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R19" s="5">
         <v>54.5</v>
       </c>
       <c r="S19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T19" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="U19" s="5">
         <v>47</v>
@@ -2250,7 +2256,7 @@
         <v>170</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AJ19" s="5">
         <v>141</v>
@@ -2270,7 +2276,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="5">
         <f t="shared" si="2"/>
@@ -2316,16 +2322,16 @@
         <v>65</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R20" s="5">
         <v>56.8</v>
       </c>
       <c r="S20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="T20" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="T20" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="U20" s="5">
         <v>49.5</v>
@@ -2364,7 +2370,7 @@
         <v>170</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AJ20" s="5">
         <v>575</v>
@@ -2384,7 +2390,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="5">
         <f t="shared" si="2"/>
@@ -2430,16 +2436,16 @@
         <v>40</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R21" s="5">
         <v>58</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U21" s="5">
         <v>52</v>
@@ -2478,7 +2484,7 @@
         <v>175</v>
       </c>
       <c r="AI21" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AJ21" s="5">
         <v>380</v>
@@ -2498,7 +2504,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="5">
         <v>80</v>
@@ -2538,16 +2544,16 @@
         <v>110</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R22" s="5">
         <v>60</v>
       </c>
       <c r="S22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="T22" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="T22" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="U22" s="5">
         <v>55</v>
@@ -2586,7 +2592,7 @@
         <v>175</v>
       </c>
       <c r="AI22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AJ22" s="5">
         <v>90</v>
@@ -2606,7 +2612,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5">
         <v>170</v>
@@ -2646,7 +2652,7 @@
         <v>175</v>
       </c>
       <c r="AI23" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AJ23" s="5">
         <v>170</v>
@@ -2668,10 +2674,10 @@
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AI25" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AJ25">
         <f t="shared" ref="AJ25:AK25" si="4">SQRT(AJ16^2 - AJ14^2)</f>
@@ -2692,13 +2698,13 @@
     </row>
     <row r="26" spans="1:39">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26">
         <v>1490</v>
       </c>
       <c r="AI26" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AJ26">
         <f t="shared" ref="AJ26:AK26" si="6">SQRT(AJ13^2 -AJ14^2)</f>
@@ -2722,7 +2728,7 @@
         <v>19</v>
       </c>
       <c r="AI27" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ27">
         <f t="shared" ref="AJ27:AK27" si="8">AJ25+AJ26</f>
@@ -2787,13 +2793,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="L29" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="AI29" s="4" t="s">
         <v>23</v>
@@ -2837,7 +2843,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="AI30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ30">
         <f t="shared" ref="AJ30:AK30" si="11">AJ21</f>
@@ -2884,16 +2890,16 @@
         <v>188</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K31" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="AI31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ31">
         <f t="shared" ref="AJ31:AM31" si="13">AJ$19*COS(AJ$10*PI()/180)</f>
@@ -2943,7 +2949,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="AI32" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AJ32">
         <v>12</v>
@@ -2978,16 +2984,16 @@
         <v>188</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K33" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="AI33" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AJ33">
         <f>AJ$32*COS(AJ$10*PI()/180)</f>
@@ -3035,7 +3041,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="AI34" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ34" s="1">
         <f>AJ17/SIN(AJ10*PI()/180)</f>
@@ -3056,16 +3062,16 @@
     </row>
     <row r="35" spans="1:39">
       <c r="A35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" t="s">
         <v>156</v>
-      </c>
-      <c r="B35" t="s">
-        <v>157</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="AI35" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AJ35">
         <f>AJ34*COS(AJ10*PI()/180)</f>
@@ -3086,16 +3092,16 @@
     </row>
     <row r="36" spans="1:39">
       <c r="A36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" t="s">
         <v>158</v>
-      </c>
-      <c r="B36" t="s">
-        <v>159</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="AI36" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AJ36">
         <f>AJ29-AJ35</f>
@@ -3116,22 +3122,22 @@
     </row>
     <row r="37" spans="1:39">
       <c r="A37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K37" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="AI37" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AJ37">
         <f>AJ$36*SIN(AJ$10*PI()/180)</f>
@@ -3155,27 +3161,27 @@
         <v>30</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="AI38" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AJ38">
         <f>AJ$36*COS(AJ$10*PI()/180)</f>
@@ -3218,16 +3224,16 @@
         <v>68.064294935470571</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="AI39" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AJ39">
         <f>AJ26+AJ30+AJ31+AJ33+AJ38+AJ34</f>
@@ -3264,13 +3270,13 @@
         <v>54</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K41" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:39">
@@ -3283,7 +3289,7 @@
       <c r="L42" s="7"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:39">
@@ -3291,16 +3297,16 @@
         <v>35</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K43" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="L43" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="AI43" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ43">
         <f>AJ15-AJ26-AJ30-AJ31-AJ33-AJ34</f>
@@ -3328,7 +3334,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="AI44" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ44">
         <f>AJ43+AJ34</f>
@@ -3352,7 +3358,7 @@
         <v>37</v>
       </c>
       <c r="AI45" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ45">
         <f>TAN(AJ10 * PI()/180) * AJ43</f>
@@ -3400,10 +3406,10 @@
         <v>39</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI47" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ47">
         <f>AJ26+AJ30+AJ31+AJ33+AJ44</f>
@@ -3432,7 +3438,7 @@
         <v>41</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3487,7 +3493,7 @@
         <v>50</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3543,7 +3549,7 @@
         <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3591,11 +3597,24 @@
         <v>64</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>161</v>
+      </c>
+      <c r="B73" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3612,11 +3631,6 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA11123-1FA4-7F4E-B60E-05994EB69497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E961EE7D-13A6-3642-B4EB-6B02739578F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2870,23 +2870,18 @@
         <v>147</v>
       </c>
       <c r="D31">
-        <f>AVERAGE(D33,C34)</f>
         <v>157</v>
       </c>
       <c r="E31">
-        <f>AVERAGE(E33,D34)</f>
         <v>165</v>
       </c>
       <c r="F31">
-        <f>AVERAGE(F33,E34)</f>
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G31">
-        <f>AVERAGE(G33,F34)</f>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31">
-        <f>AVERAGE(H33,G34)</f>
         <v>188</v>
       </c>
       <c r="J31" s="7" t="s">
@@ -2923,23 +2918,18 @@
         <v>27</v>
       </c>
       <c r="C32">
-        <f>D31</f>
         <v>157</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:G32" si="14">E31</f>
         <v>165</v>
       </c>
       <c r="E32">
-        <f t="shared" si="14"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F32">
-        <f t="shared" si="14"/>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G32">
-        <f t="shared" si="14"/>
         <v>188</v>
       </c>
       <c r="H32">
@@ -2965,24 +2955,6 @@
       </c>
     </row>
     <row r="33" spans="1:39">
-      <c r="C33">
-        <v>147</v>
-      </c>
-      <c r="D33">
-        <v>157</v>
-      </c>
-      <c r="E33">
-        <v>165</v>
-      </c>
-      <c r="F33">
-        <v>173</v>
-      </c>
-      <c r="G33">
-        <v>178</v>
-      </c>
-      <c r="H33">
-        <v>188</v>
-      </c>
       <c r="J33" s="7" t="s">
         <v>92</v>
       </c>
@@ -3004,11 +2976,11 @@
         <v>3.8076558768611051</v>
       </c>
       <c r="AL33">
-        <f t="shared" ref="AL33:AM33" si="15">AL$32*COS(AL$10*PI()/180)</f>
+        <f t="shared" ref="AL33:AM33" si="14">AL$32*COS(AL$10*PI()/180)</f>
         <v>3.8076558768611051</v>
       </c>
       <c r="AM33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.7082039324993694</v>
       </c>
     </row>
@@ -3018,24 +2990,6 @@
       </c>
       <c r="B34" t="s">
         <v>29</v>
-      </c>
-      <c r="C34">
-        <v>157</v>
-      </c>
-      <c r="D34">
-        <v>165</v>
-      </c>
-      <c r="E34">
-        <v>175</v>
-      </c>
-      <c r="F34">
-        <v>180</v>
-      </c>
-      <c r="G34">
-        <v>188</v>
-      </c>
-      <c r="H34">
-        <v>198</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -3078,15 +3032,15 @@
         <v>18.198511713310122</v>
       </c>
       <c r="AK35">
-        <f t="shared" ref="AK35:AM35" si="16">AK34*COS(AK10*PI()/180)</f>
+        <f t="shared" ref="AK35:AM35" si="15">AK34*COS(AK10*PI()/180)</f>
         <v>16.729765975103657</v>
       </c>
       <c r="AL35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>16.729765975103657</v>
       </c>
       <c r="AM35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>16.245984811645318</v>
       </c>
     </row>
@@ -3108,15 +3062,15 @@
         <v>376.8014882866899</v>
       </c>
       <c r="AK36">
-        <f t="shared" ref="AK36:AM36" si="17">AK29-AK35</f>
+        <f t="shared" ref="AK36:AM36" si="16">AK29-AK35</f>
         <v>378.27023402489635</v>
       </c>
       <c r="AL36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>378.27023402489635</v>
       </c>
       <c r="AM36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>378.75401518835469</v>
       </c>
     </row>
@@ -3144,15 +3098,15 @@
         <v>354.07757804415036</v>
       </c>
       <c r="AK37">
-        <f t="shared" ref="AK37:AM37" si="18">AK$36*SIN(AK$10*PI()/180)</f>
+        <f t="shared" ref="AK37:AM37" si="17">AK$36*SIN(AK$10*PI()/180)</f>
         <v>358.72261098619413</v>
       </c>
       <c r="AL37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>358.72261098619413</v>
       </c>
       <c r="AM37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>360.21647421783825</v>
       </c>
     </row>
@@ -3188,15 +3142,15 @@
         <v>128.873699029139</v>
       </c>
       <c r="AK38">
-        <f t="shared" ref="AK38:AM38" si="19">AK$36*COS(AK$10*PI()/180)</f>
+        <f t="shared" ref="AK38:AM38" si="18">AK$36*COS(AK$10*PI()/180)</f>
         <v>120.02690663554351</v>
       </c>
       <c r="AL38">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>120.02690663554351</v>
       </c>
       <c r="AM38">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>117.04142738094856</v>
       </c>
     </row>
@@ -3393,11 +3347,11 @@
         <v>404.32445926530335</v>
       </c>
       <c r="AL46">
-        <f t="shared" ref="AL46:AM46" si="20">SQRT(AL45^2+AL44^2)</f>
+        <f t="shared" ref="AL46:AM46" si="19">SQRT(AL45^2+AL44^2)</f>
         <v>397.67875242056454</v>
       </c>
       <c r="AM46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>403.5351597317258</v>
       </c>
     </row>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E961EE7D-13A6-3642-B4EB-6B02739578F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EEF03F-D5DB-AD4E-B692-DACA9DC8821A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="163">
   <si>
     <t>brand</t>
   </si>
@@ -357,9 +357,6 @@
   </si>
   <si>
     <t>PF</t>
-  </si>
-  <si>
-    <t>both available</t>
   </si>
   <si>
     <t>internal</t>
@@ -937,12 +934,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:39">
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:39">
@@ -950,13 +947,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>106</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:39">
@@ -1052,16 +1049,16 @@
         <v>68</v>
       </c>
       <c r="AJ8" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AK8" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="AL8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM8" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:39">
@@ -1799,7 +1796,7 @@
         <v>107.5</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AI15" s="4" t="s">
         <v>78</v>
@@ -2016,10 +2013,10 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="AC17" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD17" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="AD17" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="AE17" s="5">
         <v>80</v>
@@ -2674,10 +2671,10 @@
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AI25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AJ25">
         <f t="shared" ref="AJ25:AK25" si="4">SQRT(AJ16^2 - AJ14^2)</f>
@@ -2704,7 +2701,7 @@
         <v>1490</v>
       </c>
       <c r="AI26" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AJ26">
         <f t="shared" ref="AJ26:AK26" si="6">SQRT(AJ13^2 -AJ14^2)</f>
@@ -2728,7 +2725,7 @@
         <v>19</v>
       </c>
       <c r="AI27" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AJ27">
         <f t="shared" ref="AJ27:AK27" si="8">AJ25+AJ26</f>
@@ -2793,13 +2790,13 @@
         <v>50</v>
       </c>
       <c r="J29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="L29" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="AI29" s="4" t="s">
         <v>23</v>
@@ -2843,7 +2840,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="AI30" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ30">
         <f t="shared" ref="AJ30:AK30" si="11">AJ21</f>
@@ -2888,13 +2885,13 @@
         <v>87</v>
       </c>
       <c r="K31" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="AI31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ31">
         <f t="shared" ref="AJ31:AM31" si="13">AJ$19*COS(AJ$10*PI()/180)</f>
@@ -2939,7 +2936,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="AI32" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AJ32">
         <v>12</v>
@@ -2959,13 +2956,13 @@
         <v>92</v>
       </c>
       <c r="K33" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="AI33" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AJ33">
         <f>AJ$32*COS(AJ$10*PI()/180)</f>
@@ -2995,7 +2992,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="AI34" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ34" s="1">
         <f>AJ17/SIN(AJ10*PI()/180)</f>
@@ -3016,16 +3013,16 @@
     </row>
     <row r="35" spans="1:39">
       <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
         <v>155</v>
-      </c>
-      <c r="B35" t="s">
-        <v>156</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="AI35" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AJ35">
         <f>AJ34*COS(AJ10*PI()/180)</f>
@@ -3046,16 +3043,16 @@
     </row>
     <row r="36" spans="1:39">
       <c r="A36" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" t="s">
         <v>157</v>
-      </c>
-      <c r="B36" t="s">
-        <v>158</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="AI36" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AJ36">
         <f>AJ29-AJ35</f>
@@ -3076,22 +3073,22 @@
     </row>
     <row r="37" spans="1:39">
       <c r="A37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>95</v>
       </c>
       <c r="K37" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>118</v>
-      </c>
       <c r="AI37" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ37">
         <f>AJ$36*SIN(AJ$10*PI()/180)</f>
@@ -3120,22 +3117,22 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="AI38" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AJ38">
         <f>AJ$36*COS(AJ$10*PI()/180)</f>
@@ -3181,13 +3178,13 @@
         <v>98</v>
       </c>
       <c r="K39" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="AI39" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ39">
         <f>AJ26+AJ30+AJ31+AJ33+AJ38+AJ34</f>
@@ -3227,10 +3224,10 @@
         <v>101</v>
       </c>
       <c r="K41" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:39">
@@ -3243,7 +3240,7 @@
       <c r="L42" s="7"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:39">
@@ -3254,13 +3251,13 @@
         <v>103</v>
       </c>
       <c r="K43" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="L43" s="7" t="s">
-        <v>124</v>
-      </c>
       <c r="AI43" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ43">
         <f>AJ15-AJ26-AJ30-AJ31-AJ33-AJ34</f>
@@ -3288,7 +3285,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="AI44" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ44">
         <f>AJ43+AJ34</f>
@@ -3312,7 +3309,7 @@
         <v>37</v>
       </c>
       <c r="AI45" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AJ45">
         <f>TAN(AJ10 * PI()/180) * AJ43</f>
@@ -3359,11 +3356,12 @@
       <c r="A47" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>108</v>
-      </c>
+      <c r="B47">
+        <v>142</v>
+      </c>
+      <c r="C47" s="1"/>
       <c r="AI47" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AJ47">
         <f>AJ26+AJ30+AJ31+AJ33+AJ44</f>
@@ -3386,6 +3384,9 @@
       <c r="A48" t="s">
         <v>40</v>
       </c>
+      <c r="B48">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
@@ -3447,14 +3448,16 @@
         <v>50</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
@@ -3503,7 +3506,7 @@
         <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3551,15 +3554,15 @@
         <v>64</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>160</v>
+      </c>
+      <c r="B73" t="s">
         <v>161</v>
-      </c>
-      <c r="B73" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EEF03F-D5DB-AD4E-B692-DACA9DC8821A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08A90C8-FC1B-D54E-8FDF-6CD6AE940AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="169">
   <si>
     <t>brand</t>
   </si>
@@ -522,6 +522,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -890,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -3390,160 +3408,142 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53">
-        <v>42</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1"/>
+        <v>168</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B69">
-        <v>2399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70">
-        <v>4975</v>
+        <v>56</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>66</v>
@@ -3551,27 +3551,70 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>160</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3588,6 +3631,11 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Litespeed Flint 2025.xlsx
+++ b/data/gravel/Litespeed Flint 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08A90C8-FC1B-D54E-8FDF-6CD6AE940AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672EACC6-11AB-CB41-940D-54D74CB73F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="168">
   <si>
     <t>brand</t>
   </si>
@@ -405,9 +405,6 @@
   </si>
   <si>
     <t>188 - 198</t>
-  </si>
-  <si>
-    <t>es</t>
   </si>
   <si>
     <t>54.9**</t>
@@ -952,12 +949,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:39">
       <c r="B6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:39">
@@ -965,13 +962,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>106</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:39">
@@ -1067,16 +1064,16 @@
         <v>68</v>
       </c>
       <c r="AJ8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK8" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AK8" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="AL8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM8" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:39">
@@ -1814,7 +1811,7 @@
         <v>107.5</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AI15" s="4" t="s">
         <v>78</v>
@@ -2031,10 +2028,10 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="AC17" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD17" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="AD17" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="AE17" s="5">
         <v>80</v>
@@ -2689,10 +2686,10 @@
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AI25" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AJ25">
         <f t="shared" ref="AJ25:AK25" si="4">SQRT(AJ16^2 - AJ14^2)</f>
@@ -2719,7 +2716,7 @@
         <v>1490</v>
       </c>
       <c r="AI26" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AJ26">
         <f t="shared" ref="AJ26:AK26" si="6">SQRT(AJ13^2 -AJ14^2)</f>
@@ -2743,7 +2740,7 @@
         <v>19</v>
       </c>
       <c r="AI27" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AJ27">
         <f t="shared" ref="AJ27:AK27" si="8">AJ25+AJ26</f>
@@ -2858,7 +2855,7 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="AI30" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AJ30">
         <f t="shared" ref="AJ30:AK30" si="11">AJ21</f>
@@ -2909,7 +2906,7 @@
         <v>113</v>
       </c>
       <c r="AI31" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ31">
         <f t="shared" ref="AJ31:AM31" si="13">AJ$19*COS(AJ$10*PI()/180)</f>
@@ -2954,7 +2951,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="AI32" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AJ32">
         <v>12</v>
@@ -2980,7 +2977,7 @@
         <v>115</v>
       </c>
       <c r="AI33" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AJ33">
         <f>AJ$32*COS(AJ$10*PI()/180)</f>
@@ -3010,7 +3007,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="AI34" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ34" s="1">
         <f>AJ17/SIN(AJ10*PI()/180)</f>
@@ -3031,16 +3028,16 @@
     </row>
     <row r="35" spans="1:39">
       <c r="A35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" t="s">
         <v>154</v>
-      </c>
-      <c r="B35" t="s">
-        <v>155</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="AI35" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AJ35">
         <f>AJ34*COS(AJ10*PI()/180)</f>
@@ -3061,16 +3058,16 @@
     </row>
     <row r="36" spans="1:39">
       <c r="A36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" t="s">
         <v>156</v>
-      </c>
-      <c r="B36" t="s">
-        <v>157</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="AI36" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AJ36">
         <f>AJ29-AJ35</f>
@@ -3091,10 +3088,10 @@
     </row>
     <row r="37" spans="1:39">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>95</v>
@@ -3106,7 +3103,7 @@
         <v>117</v>
       </c>
       <c r="AI37" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AJ37">
         <f>AJ$36*SIN(AJ$10*PI()/180)</f>
@@ -3135,22 +3132,22 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="AI38" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ38">
         <f>AJ$36*COS(AJ$10*PI()/180)</f>
@@ -3202,7 +3199,7 @@
         <v>119</v>
       </c>
       <c r="AI39" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ39">
         <f>AJ26+AJ30+AJ31+AJ33+AJ38+AJ34</f>
@@ -3258,7 +3255,7 @@
       <c r="L42" s="7"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:39">
@@ -3275,7 +3272,7 @@
         <v>123</v>
       </c>
       <c r="AI43" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ43">
         <f>AJ15-AJ26-AJ30-AJ31-AJ33-AJ34</f>
@@ -3303,7 +3300,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="AI44" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AJ44">
         <f>AJ43+AJ34</f>
@@ -3327,7 +3324,7 @@
         <v>37</v>
       </c>
       <c r="AI45" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ45">
         <f>TAN(AJ10 * PI()/180) * AJ43</f>
@@ -3379,7 +3376,7 @@
       </c>
       <c r="C47" s="1"/>
       <c r="AI47" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ47">
         <f>AJ26+AJ30+AJ31+AJ33+AJ44</f>
@@ -3408,32 +3405,32 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3554,7 +3551,7 @@
         <v>58</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3602,19 +3599,24 @@
         <v>64</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" t="s">
         <v>160</v>
-      </c>
-      <c r="B79" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="L29:L30"/>
@@ -3631,11 +3633,6 @@
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="K33:K35"/>
     <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
